--- a/artfynd/A 23729-2023 artfynd.xlsx
+++ b/artfynd/A 23729-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 23729-2023 artfynd.xlsx
+++ b/artfynd/A 23729-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>109987205</v>
+        <v>109987198</v>
       </c>
       <c r="B2" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>410433.9756789801</v>
+        <v>410455</v>
       </c>
       <c r="R2" t="n">
-        <v>7045319.325871725</v>
+        <v>7045178</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2023-06-09</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-06-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>109987206</v>
+        <v>109987187</v>
       </c>
       <c r="B3" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,34 +783,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Älgtjärnen Kall, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>410432.5833704096</v>
+        <v>410533</v>
       </c>
       <c r="R3" t="n">
-        <v>7045349.277432216</v>
+        <v>7044998</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +844,14 @@
           <t>2023-06-09</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-06-09</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,15 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>109987187</v>
+        <v>109987188</v>
       </c>
       <c r="B4" t="n">
-        <v>56398</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -943,10 +917,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>410532.6766482384</v>
+        <v>410484</v>
       </c>
       <c r="R4" t="n">
-        <v>7044997.764890134</v>
+        <v>7045120</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,19 +950,9 @@
           <t>2023-06-09</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-06-09</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1020,15 +984,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>109987200</v>
+        <v>109987190</v>
       </c>
       <c r="B5" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,34 +995,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Älgtjärnen Kall, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>410521.5732683077</v>
+        <v>410452</v>
       </c>
       <c r="R5" t="n">
-        <v>7045175.332415325</v>
+        <v>7045368</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,19 +1056,14 @@
           <t>2023-06-09</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-06-09</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1129,584 +1087,6 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>109987202</v>
-      </c>
-      <c r="B6" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Älgtjärnen Kall, Jmt</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>410470.0069095299</v>
-      </c>
-      <c r="R6" t="n">
-        <v>7044995.062076448</v>
-      </c>
-      <c r="S6" t="n">
-        <v>10</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Kall</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2023-06-09</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2023-06-09</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>109987198</v>
-      </c>
-      <c r="B7" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Älgtjärnen Kall, Jmt</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>410454.5778676553</v>
-      </c>
-      <c r="R7" t="n">
-        <v>7045177.663119919</v>
-      </c>
-      <c r="S7" t="n">
-        <v>10</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Kall</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2023-06-09</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2023-06-09</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>109987188</v>
-      </c>
-      <c r="B8" t="n">
-        <v>56398</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Älgtjärnen Kall, Jmt</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>410484.2547083989</v>
-      </c>
-      <c r="R8" t="n">
-        <v>7045120.125475569</v>
-      </c>
-      <c r="S8" t="n">
-        <v>10</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Kall</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2023-06-09</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2023-06-09</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>ringhack färska</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>109987204</v>
-      </c>
-      <c r="B9" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Älgtjärnen Kall, Jmt</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>410454.7684123698</v>
-      </c>
-      <c r="R9" t="n">
-        <v>7045152.65505817</v>
-      </c>
-      <c r="S9" t="n">
-        <v>10</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Kall</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2023-06-09</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2023-06-09</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>109987190</v>
-      </c>
-      <c r="B10" t="n">
-        <v>56398</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Älgtjärnen Kall, Jmt</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>410452.3184729165</v>
-      </c>
-      <c r="R10" t="n">
-        <v>7045367.472961591</v>
-      </c>
-      <c r="S10" t="n">
-        <v>10</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Kall</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2023-06-09</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2023-06-09</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>ringhack färska</t>
-        </is>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23729-2023 artfynd.xlsx
+++ b/artfynd/A 23729-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109987198</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109987187</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -981,6 +996,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109987188</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1087,8 +1107,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109987190</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>